--- a/Data/EXCEL/Transfer/salemon/202208/8410-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8410-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C36ADDBD-C684-4D25-AF95-08B98A912E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{42666102-B21F-4FD5-8DFF-022A4B4500F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8410-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,16 +1227,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q160"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="16" width="9.5" customWidth="1"/>
-    <col min="17" max="17" width="11.125" customWidth="1"/>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="5" width="14" customWidth="1"/>
+    <col min="6" max="7" width="15.375" customWidth="1"/>
+    <col min="8" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1255,7 +1263,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1294,7 +1302,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1337,7 +1345,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1376,7 +1384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1429,7 +1437,7 @@
         <v>-0.86</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1482,7 +1490,7 @@
         <v>-1.05</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1535,7 +1543,7 @@
         <v>-1.1299999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1588,7 +1596,7 @@
         <v>-4.1399999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1641,7 +1649,7 @@
         <v>-8.77</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1694,7 +1702,7 @@
         <v>-4.9800000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1747,7 +1755,7 @@
         <v>-6.46</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1800,7 +1808,7 @@
         <v>-8.3800000000000008</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1853,7 +1861,7 @@
         <v>-9.86</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1906,7 +1914,7 @@
         <v>-8.43</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1959,7 +1967,7 @@
         <v>-9.82</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2012,7 +2020,7 @@
         <v>-8.14</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2065,7 +2073,7 @@
         <v>-4.87</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2118,7 +2126,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2171,7 +2179,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2224,7 +2232,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2277,7 +2285,7 @@
         <v>30.4</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2330,7 +2338,7 @@
         <v>42.2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2383,7 +2391,7 @@
         <v>75.2</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2436,7 +2444,7 @@
         <v>103.4</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2489,7 +2497,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2542,7 +2550,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2595,7 +2603,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2648,7 +2656,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2701,7 +2709,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2754,7 +2762,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2807,7 +2815,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2860,7 +2868,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2913,7 +2921,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2966,7 +2974,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3019,7 +3027,7 @@
         <v>-7.66</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3072,7 +3080,7 @@
         <v>-24.3</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3125,7 +3133,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3178,7 +3186,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3231,7 +3239,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3284,7 +3292,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3337,7 +3345,7 @@
         <v>-2.88</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3390,7 +3398,7 @@
         <v>-4.6100000000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3443,7 +3451,7 @@
         <v>-4.99</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3496,7 +3504,7 @@
         <v>-6.84</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3549,7 +3557,7 @@
         <v>-7.71</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3602,7 +3610,7 @@
         <v>-7.84</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3655,7 +3663,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3708,7 +3716,7 @@
         <v>6.14</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3761,7 +3769,7 @@
         <v>-1.98</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3814,7 +3822,7 @@
         <v>-0.76</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3867,7 +3875,7 @@
         <v>-0.32</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3920,7 +3928,7 @@
         <v>-2.0099999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3973,7 +3981,7 @@
         <v>-0.81</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4026,7 +4034,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4079,7 +4087,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4132,7 +4140,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4185,7 +4193,7 @@
         <v>9.7200000000000006</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4238,7 +4246,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4291,7 +4299,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4344,7 +4352,7 @@
         <v>32.799999999999997</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4397,7 +4405,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4450,7 +4458,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4503,7 +4511,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4556,7 +4564,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4609,7 +4617,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4662,7 +4670,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4715,7 +4723,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4768,7 +4776,7 @@
         <v>7.32</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4821,7 +4829,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4874,7 +4882,7 @@
         <v>-2.35</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4927,7 +4935,7 @@
         <v>-2.76</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4980,7 +4988,7 @@
         <v>-7.31</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5033,7 +5041,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5086,7 +5094,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5139,7 +5147,7 @@
         <v>33.1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5192,7 +5200,7 @@
         <v>39.9</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5245,7 +5253,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5298,7 +5306,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5351,7 +5359,7 @@
         <v>35.200000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5404,7 +5412,7 @@
         <v>36.299999999999997</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5457,7 +5465,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5510,7 +5518,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5563,7 +5571,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5616,7 +5624,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5669,7 +5677,7 @@
         <v>-30.6</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5722,7 +5730,7 @@
         <v>-31.8</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5775,7 +5783,7 @@
         <v>-34.799999999999997</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5828,7 +5836,7 @@
         <v>-37.799999999999997</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5881,7 +5889,7 @@
         <v>-40.6</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5934,7 +5942,7 @@
         <v>-41.4</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5987,7 +5995,7 @@
         <v>-43.6</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6040,7 +6048,7 @@
         <v>-41.9</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6093,7 +6101,7 @@
         <v>-36.799999999999997</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6146,7 +6154,7 @@
         <v>-31.9</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6199,7 +6207,7 @@
         <v>-31.2</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6252,7 +6260,7 @@
         <v>-27.8</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6305,7 +6313,7 @@
         <v>-15.8</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41944</v>
       </c>
@@ -6358,7 +6366,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41913</v>
       </c>
@@ -6411,7 +6419,7 @@
         <v>-13.3</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41883</v>
       </c>
@@ -6464,7 +6472,7 @@
         <v>-15.3</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41852</v>
       </c>
@@ -6517,7 +6525,7 @@
         <v>-17.5</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41821</v>
       </c>
@@ -6570,7 +6578,7 @@
         <v>-19.7</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41791</v>
       </c>
@@ -6623,7 +6631,7 @@
         <v>-14.8</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41760</v>
       </c>
@@ -6676,7 +6684,7 @@
         <v>-6.4</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41730</v>
       </c>
@@ -6729,7 +6737,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41699</v>
       </c>
@@ -6782,7 +6790,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41671</v>
       </c>
@@ -6835,7 +6843,7 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41640</v>
       </c>
@@ -6888,7 +6896,7 @@
         <v>-5.96</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41609</v>
       </c>
@@ -6941,7 +6949,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41579</v>
       </c>
@@ -6994,7 +7002,7 @@
         <v>-17.3</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41548</v>
       </c>
@@ -7047,7 +7055,7 @@
         <v>-21.3</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41518</v>
       </c>
@@ -7100,7 +7108,7 @@
         <v>-20.7</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41487</v>
       </c>
@@ -7153,7 +7161,7 @@
         <v>-18.7</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41456</v>
       </c>
@@ -7206,7 +7214,7 @@
         <v>-15.1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41426</v>
       </c>
@@ -7259,7 +7267,7 @@
         <v>-17.100000000000001</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41395</v>
       </c>
@@ -7312,7 +7320,7 @@
         <v>-25.8</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41365</v>
       </c>
@@ -7365,7 +7373,7 @@
         <v>-30.3</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41334</v>
       </c>
@@ -7418,7 +7426,7 @@
         <v>-27.2</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41306</v>
       </c>
@@ -7471,7 +7479,7 @@
         <v>-16.899999999999999</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41275</v>
       </c>
@@ -7524,7 +7532,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41244</v>
       </c>
@@ -7577,7 +7585,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41214</v>
       </c>
@@ -7630,7 +7638,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41183</v>
       </c>
@@ -7683,7 +7691,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41153</v>
       </c>
@@ -7736,7 +7744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>41122</v>
       </c>
@@ -7789,7 +7797,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>41091</v>
       </c>
@@ -7842,7 +7850,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>41061</v>
       </c>
@@ -7895,7 +7903,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>41030</v>
       </c>
@@ -7948,7 +7956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>41000</v>
       </c>
@@ -8001,7 +8009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40969</v>
       </c>
@@ -8054,7 +8062,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>40940</v>
       </c>
@@ -8107,7 +8115,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="5" customFormat="1">
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>40909</v>
       </c>
@@ -8160,7 +8168,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="5" customFormat="1">
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>40878</v>
       </c>
@@ -8213,7 +8221,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="5" customFormat="1">
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>40848</v>
       </c>
@@ -8266,7 +8274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:17" s="5" customFormat="1">
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>40817</v>
       </c>
@@ -8319,7 +8327,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="5" customFormat="1">
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>40787</v>
       </c>
@@ -8372,7 +8380,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="5" customFormat="1">
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>40756</v>
       </c>
@@ -8425,7 +8433,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="5" customFormat="1">
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>40725</v>
       </c>
@@ -8478,7 +8486,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:17" s="5" customFormat="1">
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>40695</v>
       </c>
@@ -8531,7 +8539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:17" s="5" customFormat="1">
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>40664</v>
       </c>
@@ -8584,7 +8592,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:17" s="5" customFormat="1">
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>40634</v>
       </c>
@@ -8637,7 +8645,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="1:17" s="5" customFormat="1">
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>40603</v>
       </c>
@@ -8690,7 +8698,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:17" s="5" customFormat="1">
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>40575</v>
       </c>
@@ -8743,7 +8751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" s="5" customFormat="1">
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>40544</v>
       </c>
@@ -8796,7 +8804,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="5" customFormat="1">
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>40513</v>
       </c>
@@ -8849,7 +8857,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" s="5" customFormat="1">
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>40483</v>
       </c>
@@ -8902,7 +8910,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="5" customFormat="1">
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>40452</v>
       </c>
@@ -8955,7 +8963,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:17" s="5" customFormat="1">
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>40422</v>
       </c>
@@ -9008,7 +9016,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:17" s="5" customFormat="1">
+    <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>40391</v>
       </c>
@@ -9061,7 +9069,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:17" s="5" customFormat="1">
+    <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>40360</v>
       </c>
@@ -9114,7 +9122,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:17" s="5" customFormat="1">
+    <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>40330</v>
       </c>
@@ -9167,7 +9175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:17" s="5" customFormat="1">
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>40299</v>
       </c>
@@ -9220,7 +9228,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:17" s="5" customFormat="1">
+    <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>40269</v>
       </c>
@@ -9273,7 +9281,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:17" s="5" customFormat="1">
+    <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>40238</v>
       </c>
@@ -9326,7 +9334,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:17" s="5" customFormat="1">
+    <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>40210</v>
       </c>
@@ -9379,7 +9387,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:17" s="5" customFormat="1">
+    <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>40179</v>
       </c>
@@ -9432,7 +9440,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:17" s="5" customFormat="1">
+    <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>40148</v>
       </c>
@@ -9485,7 +9493,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:17" s="5" customFormat="1">
+    <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>40118</v>
       </c>
@@ -9538,7 +9546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17" s="5" customFormat="1">
+    <row r="159" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>40087</v>
       </c>
@@ -9591,7 +9599,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:17" s="5" customFormat="1">
+    <row r="160" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>40057</v>
       </c>
@@ -9659,7 +9667,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>